--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-12-2025.xlsx
@@ -538,17 +538,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£9.71</t>
+          <t>£9.69</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£9.71</t>
+          <t>£9.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£9.71</t>
+          <t>£9.69</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1618,17 +1618,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.12</t>
+          <t>£24.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.12</t>
+          <t>£24.97</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.12</t>
+          <t>£24.97</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£42.88</t>
+          <t>£40.93</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c4b9a235
-	0x7ff7c48f2630
-	0x7ff7c46816dd
-	0x7ff7c46da27e
-	0x7ff7c46da58c
-	0x7ff7c472ed77
-	0x7ff7c472baba
-	0x7ff7c46cb0ed
-	0x7ff7c46cbf63
-	0x7ff7c4bc5d60
-	0x7ff7c4bbfe8a
-	0x7ff7c4be1005
-	0x7ff7c490d71e
-	0x7ff7c4914e1f
-	0x7ff7c48fb7c4
-	0x7ff7c48fb97f
-	0x7ff7c48e18e8
+	0x7ff664d7a235
+	0x7ff664ad2630
+	0x7ff6648616dd
+	0x7ff6648ba27e
+	0x7ff6648ba58c
+	0x7ff66490ed77
+	0x7ff66490baba
+	0x7ff6648ab0ed
+	0x7ff6648abf63
+	0x7ff664da5d60
+	0x7ff664d9fe8a
+	0x7ff664dc1005
+	0x7ff664aed71e
+	0x7ff664af4e1f
+	0x7ff664adb7c4
+	0x7ff664adb97f
+	0x7ff664ac18e8
 	0x7ffeb4f2e8d7
 	0x7ffeb602c53c
 </t>
